--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -38073,6 +38073,405 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>8233</v>
+      </c>
+      <c r="O195" t="n">
+        <v>8233</v>
+      </c>
+      <c r="P195" t="n">
+        <v>8233</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6.724783619488954</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>8233</v>
+      </c>
+      <c r="O196" t="n">
+        <v>8233</v>
+      </c>
+      <c r="P196" t="n">
+        <v>8233</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38106,7 +38505,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -38189,7 +38588,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -38199,7 +38598,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -38219,7 +38618,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -38251,7 +38650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2194060</v>
+        <v>2202293</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -36505,12 +36505,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -36535,7 +36535,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -36544,73 +36544,59 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>7724</v>
+        <v>148205</v>
       </c>
       <c r="O187" t="n">
-        <v>7724</v>
-      </c>
-      <c r="P187" t="n">
-        <v>7724</v>
+        <v>148205</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>6.309028140037978</v>
+        <v>10.48931433314107</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -36620,22 +36606,22 @@
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -36662,7 +36648,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -36714,98 +36700,23 @@
       <c r="P188" t="n">
         <v>7724</v>
       </c>
+      <c r="R188" t="n">
+        <v>6.309028140037978</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -36899,7 +36810,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -36934,7 +36845,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -36943,31 +36854,106 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>7674</v>
+        <v>7724</v>
       </c>
       <c r="O189" t="n">
-        <v>7674</v>
+        <v>7724</v>
       </c>
       <c r="P189" t="n">
-        <v>7674</v>
-      </c>
-      <c r="R189" t="n">
-        <v>6.26818771965969</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7724</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -37061,7 +37047,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -37113,98 +37099,23 @@
       <c r="P190" t="n">
         <v>7674</v>
       </c>
+      <c r="R190" t="n">
+        <v>6.26818771965969</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -37298,7 +37209,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -37333,7 +37244,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -37342,31 +37253,106 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>4432</v>
+        <v>7674</v>
       </c>
       <c r="O191" t="n">
-        <v>4432</v>
+        <v>7674</v>
       </c>
       <c r="P191" t="n">
-        <v>4432</v>
-      </c>
-      <c r="R191" t="n">
-        <v>3.620094862331476</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7674</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -37460,7 +37446,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -37512,98 +37498,23 @@
       <c r="P192" t="n">
         <v>4432</v>
       </c>
+      <c r="R192" t="n">
+        <v>3.620094862331476</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -37697,7 +37608,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -37732,7 +37643,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -37741,31 +37652,106 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>7284</v>
+        <v>4432</v>
       </c>
       <c r="O193" t="n">
-        <v>7284</v>
+        <v>4432</v>
       </c>
       <c r="P193" t="n">
-        <v>7284</v>
-      </c>
-      <c r="R193" t="n">
-        <v>5.949632440709042</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4432</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -37859,7 +37845,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -37911,98 +37897,23 @@
       <c r="P194" t="n">
         <v>7284</v>
       </c>
+      <c r="R194" t="n">
+        <v>5.949632440709042</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -38096,7 +38007,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -38131,7 +38042,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -38140,31 +38051,106 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>8233</v>
+        <v>7284</v>
       </c>
       <c r="O195" t="n">
-        <v>8233</v>
+        <v>7284</v>
       </c>
       <c r="P195" t="n">
-        <v>8233</v>
-      </c>
-      <c r="R195" t="n">
-        <v>6.724783619488954</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7284</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -38258,7 +38244,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -38310,98 +38296,23 @@
       <c r="P196" t="n">
         <v>8233</v>
       </c>
+      <c r="R196" t="n">
+        <v>6.724783619488954</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -38467,6 +38378,243 @@
         </is>
       </c>
       <c r="BC196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>8233</v>
+      </c>
+      <c r="O197" t="n">
+        <v>8233</v>
+      </c>
+      <c r="P197" t="n">
+        <v>8233</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -38588,7 +38736,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -38598,7 +38746,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -38650,7 +38798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2202293</v>
+        <v>2350498</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -38620,6 +38620,405 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>8679</v>
+      </c>
+      <c r="O198" t="n">
+        <v>8679</v>
+      </c>
+      <c r="P198" t="n">
+        <v>8679</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7.089080169263286</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>8679</v>
+      </c>
+      <c r="O199" t="n">
+        <v>8679</v>
+      </c>
+      <c r="P199" t="n">
+        <v>8679</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38653,7 +39052,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -38736,7 +39135,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -38746,7 +39145,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -38766,7 +39165,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -38798,7 +39197,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2350498</v>
+        <v>2359177</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20719,7 +20719,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30371,7 +30371,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30770,7 +30770,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31568,7 +31568,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -35195,7 +35195,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35594,7 +35594,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35993,7 +35993,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37338,7 +37338,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38934,7 +38934,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39014,6 +39014,405 @@
         </is>
       </c>
       <c r="BC199" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>8555</v>
+      </c>
+      <c r="O200" t="n">
+        <v>8555</v>
+      </c>
+      <c r="P200" t="n">
+        <v>8555</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6.987795926725131</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>8555</v>
+      </c>
+      <c r="O201" t="n">
+        <v>8555</v>
+      </c>
+      <c r="P201" t="n">
+        <v>8555</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -39052,7 +39451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -39145,7 +39544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -39165,7 +39564,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -39197,7 +39596,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2359177</v>
+        <v>2367732</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -32599,12 +32599,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -32638,10 +32638,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>19092</v>
+        <v>2993</v>
       </c>
       <c r="O167" t="n">
-        <v>19092</v>
+        <v>2993</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
@@ -32750,12 +32750,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -32789,10 +32789,10 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>19092</v>
+        <v>2993</v>
       </c>
       <c r="O168" t="n">
-        <v>19092</v>
+        <v>2993</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -32947,7 +32947,7 @@
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
@@ -32984,12 +32984,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -33023,10 +33023,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>3589</v>
+        <v>19092</v>
       </c>
       <c r="O169" t="n">
-        <v>3589</v>
+        <v>19092</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
@@ -33135,12 +33135,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -33174,10 +33174,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>3589</v>
+        <v>19092</v>
       </c>
       <c r="O170" t="n">
-        <v>3589</v>
+        <v>19092</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
@@ -33369,12 +33369,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -33408,10 +33408,10 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>2443</v>
+        <v>3589</v>
       </c>
       <c r="O171" t="n">
-        <v>2443</v>
+        <v>3589</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
@@ -33520,12 +33520,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -33559,10 +33559,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>2443</v>
+        <v>3589</v>
       </c>
       <c r="O172" t="n">
-        <v>2443</v>
+        <v>3589</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -33717,7 +33717,7 @@
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
@@ -33754,12 +33754,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -33793,10 +33793,10 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1763</v>
+        <v>2443</v>
       </c>
       <c r="O173" t="n">
-        <v>1763</v>
+        <v>2443</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
@@ -33905,12 +33905,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -33944,10 +33944,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1763</v>
+        <v>2443</v>
       </c>
       <c r="O174" t="n">
-        <v>1763</v>
+        <v>2443</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -34102,7 +34102,7 @@
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
@@ -34139,12 +34139,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -34178,10 +34178,10 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>14118</v>
+        <v>1763</v>
       </c>
       <c r="O175" t="n">
-        <v>14118</v>
+        <v>1763</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
@@ -34290,12 +34290,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -34329,10 +34329,10 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>14118</v>
+        <v>1763</v>
       </c>
       <c r="O176" t="n">
-        <v>14118</v>
+        <v>1763</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -34487,7 +34487,7 @@
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
@@ -34524,12 +34524,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -34563,10 +34563,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1699</v>
+        <v>14118</v>
       </c>
       <c r="O177" t="n">
-        <v>1699</v>
+        <v>14118</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
@@ -34675,12 +34675,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -34714,10 +34714,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>1699</v>
+        <v>14118</v>
       </c>
       <c r="O178" t="n">
-        <v>1699</v>
+        <v>14118</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -34872,7 +34872,7 @@
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
@@ -34909,12 +34909,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -34939,7 +34939,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -34948,30 +34948,19 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>10023</v>
+        <v>1699</v>
       </c>
       <c r="O179" t="n">
-        <v>10023</v>
-      </c>
-      <c r="P179" t="n">
-        <v>10023</v>
-      </c>
-      <c r="R179" t="n">
-        <v>8.186870669031675</v>
+        <v>1699</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -34981,7 +34970,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -34991,55 +34980,55 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -35071,12 +35060,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -35101,7 +35090,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -35110,47 +35099,44 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>10023</v>
+        <v>1699</v>
       </c>
       <c r="O180" t="n">
-        <v>10023</v>
-      </c>
-      <c r="P180" t="n">
-        <v>10023</v>
+        <v>1699</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
@@ -35160,7 +35146,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -35175,7 +35161,7 @@
       </c>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG180" t="inlineStr">
@@ -35195,17 +35181,17 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -35218,7 +35204,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
@@ -35228,55 +35214,55 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -35338,7 +35324,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -35347,16 +35333,16 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="O181" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="P181" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="R181" t="n">
-        <v>7.897720492753394</v>
+        <v>8.186870669031675</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -35500,7 +35486,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -35509,13 +35495,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="O182" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="P182" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -35737,7 +35723,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -35746,16 +35732,16 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="O183" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="P183" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="R183" t="n">
-        <v>7.363527794205384</v>
+        <v>7.897720492753394</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -35899,7 +35885,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -35908,13 +35894,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="O184" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="P184" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -36136,7 +36122,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -36145,16 +36131,16 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="O185" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="P185" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="R185" t="n">
-        <v>5.885921384918912</v>
+        <v>7.363527794205384</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -36298,7 +36284,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -36307,13 +36293,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="O186" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="P186" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -36505,12 +36491,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -36535,68 +36521,82 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N187" t="n">
-        <v>148205</v>
+        <v>7206</v>
       </c>
       <c r="O187" t="n">
-        <v>148205</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
+        <v>7206</v>
+      </c>
+      <c r="P187" t="n">
+        <v>7206</v>
       </c>
       <c r="R187" t="n">
-        <v>10.48931433314107</v>
+        <v>5.885921384918912</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -36606,22 +36606,22 @@
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36648,7 +36648,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -36683,40 +36683,115 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N188" t="n">
-        <v>7724</v>
+        <v>7206</v>
       </c>
       <c r="O188" t="n">
-        <v>7724</v>
+        <v>7206</v>
       </c>
       <c r="P188" t="n">
-        <v>7724</v>
-      </c>
-      <c r="R188" t="n">
-        <v>6.309028140037978</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7206</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -36810,17 +36885,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -36845,7 +36920,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -36854,148 +36929,59 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>7724</v>
+        <v>148205</v>
       </c>
       <c r="O189" t="n">
-        <v>7724</v>
-      </c>
-      <c r="P189" t="n">
-        <v>7724</v>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
+        <v>148205</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>10.48931433314107</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -37005,22 +36991,22 @@
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -37052,12 +37038,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -37082,7 +37068,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -37091,30 +37077,19 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>7674</v>
+        <v>4236</v>
       </c>
       <c r="O190" t="n">
-        <v>7674</v>
-      </c>
-      <c r="P190" t="n">
-        <v>7674</v>
-      </c>
-      <c r="R190" t="n">
-        <v>6.26818771965969</v>
+        <v>4236</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -37124,7 +37099,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -37134,55 +37109,55 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -37214,12 +37189,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -37244,7 +37219,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -37253,47 +37228,44 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>7674</v>
+        <v>4236</v>
       </c>
       <c r="O191" t="n">
-        <v>7674</v>
-      </c>
-      <c r="P191" t="n">
-        <v>7674</v>
+        <v>4236</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
@@ -37303,7 +37275,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -37318,7 +37290,7 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG191" t="inlineStr">
@@ -37338,17 +37310,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -37361,7 +37333,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -37371,55 +37343,55 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -37451,12 +37423,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -37481,7 +37453,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -37490,30 +37462,19 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>4432</v>
+        <v>21919</v>
       </c>
       <c r="O192" t="n">
-        <v>4432</v>
-      </c>
-      <c r="P192" t="n">
-        <v>4432</v>
-      </c>
-      <c r="R192" t="n">
-        <v>3.620094862331476</v>
+        <v>21919</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -37523,7 +37484,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -37533,55 +37494,55 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -37613,12 +37574,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -37643,7 +37604,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -37652,47 +37613,44 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>4432</v>
+        <v>21919</v>
       </c>
       <c r="O193" t="n">
-        <v>4432</v>
-      </c>
-      <c r="P193" t="n">
-        <v>4432</v>
+        <v>21919</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
@@ -37702,7 +37660,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -37717,7 +37675,7 @@
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG193" t="inlineStr">
@@ -37737,17 +37695,17 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37760,7 +37718,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
@@ -37770,55 +37728,55 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -37850,12 +37808,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -37880,7 +37838,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -37889,30 +37847,19 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>7284</v>
+        <v>3754</v>
       </c>
       <c r="O194" t="n">
-        <v>7284</v>
-      </c>
-      <c r="P194" t="n">
-        <v>7284</v>
-      </c>
-      <c r="R194" t="n">
-        <v>5.949632440709042</v>
+        <v>3754</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -37922,7 +37869,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -37932,55 +37879,55 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -38012,12 +37959,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -38042,7 +37989,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -38051,47 +37998,44 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>7284</v>
+        <v>3754</v>
       </c>
       <c r="O195" t="n">
-        <v>7284</v>
-      </c>
-      <c r="P195" t="n">
-        <v>7284</v>
+        <v>3754</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
@@ -38101,7 +38045,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -38116,7 +38060,7 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG195" t="inlineStr">
@@ -38136,17 +38080,17 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38159,7 +38103,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -38169,55 +38113,55 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -38249,12 +38193,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -38279,7 +38223,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -38288,30 +38232,19 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>8233</v>
+        <v>2636</v>
       </c>
       <c r="O196" t="n">
-        <v>8233</v>
-      </c>
-      <c r="P196" t="n">
-        <v>8233</v>
-      </c>
-      <c r="R196" t="n">
-        <v>6.724783619488954</v>
+        <v>2636</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -38321,7 +38254,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -38331,55 +38264,55 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -38411,12 +38344,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -38441,7 +38374,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -38450,47 +38383,44 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>8233</v>
+        <v>2636</v>
       </c>
       <c r="O197" t="n">
-        <v>8233</v>
-      </c>
-      <c r="P197" t="n">
-        <v>8233</v>
+        <v>2636</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
@@ -38500,7 +38430,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -38515,7 +38445,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -38535,17 +38465,17 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -38558,7 +38488,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -38568,55 +38498,55 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -38648,12 +38578,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -38678,39 +38608,28 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>8679</v>
+        <v>2268</v>
       </c>
       <c r="O198" t="n">
-        <v>8679</v>
-      </c>
-      <c r="P198" t="n">
-        <v>8679</v>
-      </c>
-      <c r="R198" t="n">
-        <v>7.089080169263286</v>
+        <v>2268</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -38720,7 +38639,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -38730,55 +38649,55 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -38810,12 +38729,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -38840,56 +38759,53 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>8679</v>
+        <v>2268</v>
       </c>
       <c r="O199" t="n">
-        <v>8679</v>
-      </c>
-      <c r="P199" t="n">
-        <v>8679</v>
+        <v>2268</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
@@ -38899,7 +38815,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -38914,7 +38830,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
@@ -38934,17 +38850,17 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -38957,7 +38873,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -38967,55 +38883,55 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39047,12 +38963,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -39077,39 +38993,28 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>8555</v>
+        <v>14795</v>
       </c>
       <c r="O200" t="n">
-        <v>8555</v>
-      </c>
-      <c r="P200" t="n">
-        <v>8555</v>
-      </c>
-      <c r="R200" t="n">
-        <v>6.987795926725131</v>
+        <v>14795</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -39119,7 +39024,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -39129,55 +39034,55 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39209,12 +39114,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -39239,56 +39144,53 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N201" t="n">
-        <v>8555</v>
+        <v>14795</v>
       </c>
       <c r="O201" t="n">
-        <v>8555</v>
-      </c>
-      <c r="P201" t="n">
-        <v>8555</v>
+        <v>14795</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis</t>
+          <t>其他感染性腹泻病</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
@@ -39298,7 +39200,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -39313,7 +39215,7 @@
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG201" t="inlineStr">
@@ -39333,17 +39235,17 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -39356,63 +39258,3241 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>1702</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1702</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>1702</v>
+      </c>
+      <c r="O203" t="n">
+        <v>1702</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_INFECTIOUS_DIARRHEA; SER_CN_PROV_REPORT_INFECTIOUS_DIARRHEA</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O204" t="n">
+        <v>7724</v>
+      </c>
+      <c r="P204" t="n">
+        <v>7724</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6.309028140037978</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ201" t="inlineStr">
+      <c r="AQ204" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS201" t="inlineStr">
+      <c r="AS204" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="AT201" t="n">
+      <c r="AT204" t="n">
         <v>1</v>
       </c>
-      <c r="AU201" t="inlineStr">
+      <c r="AU204" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV201" t="inlineStr">
+      <c r="AV204" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW201" t="inlineStr">
+      <c r="AW204" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX201" t="inlineStr">
+      <c r="AX204" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY201" t="inlineStr">
+      <c r="AY204" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ201" t="inlineStr">
+      <c r="AZ204" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA201" t="inlineStr">
+      <c r="BA204" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB201" t="inlineStr">
+      <c r="BB204" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC201" t="inlineStr">
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O205" t="n">
+        <v>7724</v>
+      </c>
+      <c r="P205" t="n">
+        <v>7724</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>7674</v>
+      </c>
+      <c r="O206" t="n">
+        <v>7674</v>
+      </c>
+      <c r="P206" t="n">
+        <v>7674</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6.26818771965969</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>7674</v>
+      </c>
+      <c r="O207" t="n">
+        <v>7674</v>
+      </c>
+      <c r="P207" t="n">
+        <v>7674</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>4432</v>
+      </c>
+      <c r="O208" t="n">
+        <v>4432</v>
+      </c>
+      <c r="P208" t="n">
+        <v>4432</v>
+      </c>
+      <c r="R208" t="n">
+        <v>3.620094862331476</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>4432</v>
+      </c>
+      <c r="O209" t="n">
+        <v>4432</v>
+      </c>
+      <c r="P209" t="n">
+        <v>4432</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>7284</v>
+      </c>
+      <c r="O210" t="n">
+        <v>7284</v>
+      </c>
+      <c r="P210" t="n">
+        <v>7284</v>
+      </c>
+      <c r="R210" t="n">
+        <v>5.949632440709042</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>7284</v>
+      </c>
+      <c r="O211" t="n">
+        <v>7284</v>
+      </c>
+      <c r="P211" t="n">
+        <v>7284</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>8233</v>
+      </c>
+      <c r="O212" t="n">
+        <v>8233</v>
+      </c>
+      <c r="P212" t="n">
+        <v>8233</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6.724783619488954</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>8233</v>
+      </c>
+      <c r="O213" t="n">
+        <v>8233</v>
+      </c>
+      <c r="P213" t="n">
+        <v>8233</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>8679</v>
+      </c>
+      <c r="O214" t="n">
+        <v>8679</v>
+      </c>
+      <c r="P214" t="n">
+        <v>8679</v>
+      </c>
+      <c r="R214" t="n">
+        <v>7.089080169263286</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>8679</v>
+      </c>
+      <c r="O215" t="n">
+        <v>8679</v>
+      </c>
+      <c r="P215" t="n">
+        <v>8679</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>8555</v>
+      </c>
+      <c r="O216" t="n">
+        <v>8555</v>
+      </c>
+      <c r="P216" t="n">
+        <v>8555</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6.987795926725131</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>8555</v>
+      </c>
+      <c r="O217" t="n">
+        <v>8555</v>
+      </c>
+      <c r="P217" t="n">
+        <v>8555</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -39534,7 +42614,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -39544,7 +42624,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -39564,7 +42644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -39596,7 +42676,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2367732</v>
+        <v>2422035</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -42498,6 +42498,405 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>8300</v>
+      </c>
+      <c r="O218" t="n">
+        <v>8300</v>
+      </c>
+      <c r="P218" t="n">
+        <v>8300</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6.779509782795861</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>8300</v>
+      </c>
+      <c r="O219" t="n">
+        <v>8300</v>
+      </c>
+      <c r="P219" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42531,7 +42930,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -42614,7 +43013,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -42624,7 +43023,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -42644,7 +43043,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -42676,7 +43075,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2422035</v>
+        <v>2430335</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -42897,6 +42897,405 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>4990</v>
+      </c>
+      <c r="O220" t="n">
+        <v>4990</v>
+      </c>
+      <c r="P220" t="n">
+        <v>4990</v>
+      </c>
+      <c r="R220" t="n">
+        <v>4.075873953753174</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>4990</v>
+      </c>
+      <c r="O221" t="n">
+        <v>4990</v>
+      </c>
+      <c r="P221" t="n">
+        <v>4990</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42930,7 +43329,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43013,7 +43412,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -43023,7 +43422,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -43043,7 +43442,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -43075,7 +43474,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2430335</v>
+        <v>2435325</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5994,6 +5999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11215,6 +11225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16453,6 +16468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21289,6 +21309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26912,6 +26937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31736,6 +31766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36943,6 +36978,11 @@
       <c r="S189" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -43336,6 +43336,405 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>7373</v>
+      </c>
+      <c r="O222" t="n">
+        <v>7373</v>
+      </c>
+      <c r="P222" t="n">
+        <v>7373</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6.022328388982395</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>7373</v>
+      </c>
+      <c r="O223" t="n">
+        <v>7373</v>
+      </c>
+      <c r="P223" t="n">
+        <v>7373</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43369,7 +43768,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43851,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -43462,7 +43861,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -43482,7 +43881,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -43514,7 +43913,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2435325</v>
+        <v>2442698</v>
       </c>
     </row>
     <row r="16">
